--- a/Assignment 2.xlsx
+++ b/Assignment 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\ere\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\awfe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950E7557-5961-4F8F-958F-806BB9702CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CC941E-16C6-47D9-BCF1-D274CA03663F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment generation" sheetId="1" r:id="rId1"/>
@@ -563,18 +563,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -583,10 +577,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1393,7 +1393,7 @@
   <cols>
     <col min="1" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="37.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="27.5703125" customWidth="1"/>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="47"/>
+      <c r="E2" s="41"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1425,7 +1425,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="40"/>
+      <c r="E3" s="39"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="47"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -1458,7 +1458,7 @@
     <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="47"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -1492,7 +1492,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="39"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="45"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
@@ -1529,11 +1529,11 @@
     <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="40"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="40"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="47"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -1569,7 +1569,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="40"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="47"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -1609,7 +1609,7 @@
     <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="40"/>
+      <c r="E18" s="39"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -1630,18 +1630,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="41" t="s">
+      <c r="E20" s="41"/>
+      <c r="F20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44" t="s">
+      <c r="G20" s="45"/>
+      <c r="H20" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="43"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -1650,11 +1650,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="43"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="40"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -1672,25 +1672,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="47"/>
+      <c r="E23" s="41"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="44" t="s">
+      <c r="L23" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="45"/>
+      <c r="M23" s="43"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
+      <c r="E24" s="39"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1698,7 +1698,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="40"/>
+      <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -1711,10 +1711,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="45"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -1726,7 +1726,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="40"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -1744,15 +1744,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="45"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="47"/>
+      <c r="E29" s="41"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="40"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -1785,44 +1785,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="47"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="41" t="s">
+      <c r="E32" s="41"/>
+      <c r="F32" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="46" t="s">
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="47"/>
+      <c r="M32" s="41"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="39"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="43"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="45"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="39"/>
+      <c r="M33" s="46"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -1834,33 +1834,46 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="45"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="40"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="39"/>
+      <c r="I38" s="46"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -1877,25 +1890,12 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Assignment 2.xlsx
+++ b/Assignment 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\awfe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\edw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CC941E-16C6-47D9-BCF1-D274CA03663F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7FE914-1347-4332-967A-5DFC248AE354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment generation" sheetId="1" r:id="rId1"/>
@@ -563,12 +563,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -577,16 +583,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -623,22 +623,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>201706</xdr:rowOff>
+      <xdr:colOff>340179</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>13608</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>776386</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1640182</xdr:rowOff>
+      <xdr:colOff>1347593</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5102680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C443CF35-4AE0-4DC9-801B-A9718B044E23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57F6AD57-93B2-85C2-641E-3D06FE19704F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -654,8 +654,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2386853" y="6017559"/>
-          <a:ext cx="2715004" cy="1438476"/>
+          <a:off x="2177143" y="340179"/>
+          <a:ext cx="3511129" cy="5089072"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -667,22 +667,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>421821</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1036813</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1725707</xdr:rowOff>
+      <xdr:colOff>2332722</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>2068286</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76A3737C-B25E-4F39-81CF-1B38D7A82DB8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACA25600-7876-3F44-2D2E-523A92611160}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -698,8 +698,272 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1815353" y="313766"/>
-          <a:ext cx="3546931" cy="1725706"/>
+          <a:off x="2258785" y="6068785"/>
+          <a:ext cx="4414616" cy="1850572"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>163284</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1115784</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>5136544</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{941DF547-9ABB-BBB3-93FA-E486D279FCFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000248" y="8558893"/>
+          <a:ext cx="3456215" cy="5136544"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>843643</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>5179932</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0693C63-0EBC-4FD0-B6F7-89300E448DC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9933214" y="14165036"/>
+          <a:ext cx="2598965" cy="5098289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2811905</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>2558143</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E9FD53A-5D4F-3E2A-CB43-716C15C291EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836964" y="14083393"/>
+          <a:ext cx="5315620" cy="2558143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1809749</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>80760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2529FA9-F702-97A0-205F-881B84B37F84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1973035" y="19648714"/>
+          <a:ext cx="4177393" cy="5237867"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>13606</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1115785</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>5191553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89A782D4-1425-E760-88EE-37A34DEE3A75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1850571" y="25145999"/>
+          <a:ext cx="3605893" cy="5177947"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>612320</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>952499</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>5166151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A58B7A1-7D88-23CC-008D-30A806997C14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836963" y="30656893"/>
+          <a:ext cx="3456215" cy="5166151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1410,10 +1674,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="41"/>
+      <c r="E2" s="47"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1425,7 +1689,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -1445,20 +1709,20 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="41"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
       <c r="L5" s="14"/>
       <c r="M5" s="11"/>
     </row>
-    <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:13" ht="180.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="39"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -1478,10 +1742,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="41"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -1492,7 +1756,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
+      <c r="E9" s="40"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -1512,28 +1776,28 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="41"/>
+      <c r="E11" s="47"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="43"/>
+      <c r="I11" s="45"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
     </row>
-    <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -1553,10 +1817,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="41"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -1569,7 +1833,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -1593,10 +1857,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="41"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -1606,10 +1870,10 @@
       <c r="L17" s="14"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -1630,18 +1894,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="44" t="s">
+      <c r="E20" s="47"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="42" t="s">
+      <c r="G20" s="43"/>
+      <c r="H20" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="43"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -1650,11 +1914,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -1672,25 +1936,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="41"/>
+      <c r="E23" s="47"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="43"/>
+      <c r="M23" s="45"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1698,7 +1962,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
+      <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -1711,10 +1975,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="43"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -1726,7 +1990,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -1744,15 +2008,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="43"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="41"/>
+      <c r="E29" s="47"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -1764,10 +2028,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -1785,44 +2049,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="41"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="44" t="s">
+      <c r="E32" s="47"/>
+      <c r="F32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="40" t="s">
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="41"/>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="46"/>
+      <c r="B33" s="39"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="45"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="46"/>
+      <c r="M33" s="39"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -1834,46 +2098,33 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="43"/>
+      <c r="E35" s="45"/>
       <c r="F35" s="11"/>
     </row>
-    <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="46"/>
+      <c r="I38" s="39"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -1890,12 +2141,25 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Assignment 2.xlsx
+++ b/Assignment 2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\edw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\aasd\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7FE914-1347-4332-967A-5DFC248AE354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -563,18 +563,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -583,10 +577,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="47"/>
+      <c r="E2" s="41"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1689,7 +1689,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="40"/>
+      <c r="E3" s="39"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="47"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -1722,7 +1722,7 @@
     <row r="6" spans="3:13" ht="180.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="47"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -1756,7 +1756,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="39"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -1776,16 +1776,16 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="45"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
@@ -1793,11 +1793,11 @@
     <row r="12" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="40"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="40"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="47"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -1833,7 +1833,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="40"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="47"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -1873,7 +1873,7 @@
     <row r="18" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="40"/>
+      <c r="E18" s="39"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -1894,18 +1894,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="41" t="s">
+      <c r="E20" s="41"/>
+      <c r="F20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44" t="s">
+      <c r="G20" s="45"/>
+      <c r="H20" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="43"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -1914,11 +1914,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="43"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="40"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -1936,25 +1936,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="47"/>
+      <c r="E23" s="41"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="44" t="s">
+      <c r="L23" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="45"/>
+      <c r="M23" s="43"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
+      <c r="E24" s="39"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1962,7 +1962,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="40"/>
+      <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -1975,10 +1975,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="45"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -1990,7 +1990,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="40"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -2008,15 +2008,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="45"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="47"/>
+      <c r="E29" s="41"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="40"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -2049,44 +2049,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="47"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="41" t="s">
+      <c r="E32" s="41"/>
+      <c r="F32" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="46" t="s">
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="47"/>
+      <c r="M32" s="41"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="39"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="43"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="45"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="39"/>
+      <c r="M33" s="46"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -2098,33 +2098,46 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="45"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="40"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="39"/>
+      <c r="I38" s="46"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -2141,25 +2154,12 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
